--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.092.019-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.504.980-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.092.019-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>77.430.680-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1063,7 +1079,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2268-33-CM25</t>
+          <t>1314-26-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1104,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1119,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MAGNET S.P.A.</t>
+          <t>WAYS ASESORIAS LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.224.628-7</t>
+          <t>76.400.403-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1134,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>248945.81</v>
+        <v>19775.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2686-117-CM25</t>
+          <t>2268-33-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1165,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.071.500-7</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLINA</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1180,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>MAGNET S.P.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.224.628-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1195,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>28369.4</v>
+        <v>248945.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1314-26-CM25</t>
+          <t>2686-117-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1226,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.071.500-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1241,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAYS ASESORIAS LIMITADA</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.400.403-5</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1256,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>19775.64</v>
+        <v>28369.4</v>
       </c>
     </row>
     <row r="14">
@@ -1355,7 +1371,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1368,7 +1388,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>585-41-CM25</t>
+          <t>1057495-416-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1408,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.608.104-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL LUCIO CORDOVA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,28 +1428,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NOVIS</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.967.100-k</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28905.3</v>
+        <v>12161.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057495-416-CM25</t>
+          <t>1314-29-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1473,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.608.104-7</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL LUCIO CORDOVA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1493,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>52.004.665-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12161.15</v>
+        <v>19489.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1314-29-CM25</t>
+          <t>1057387-140-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,17 +1538,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,28 +1558,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>G-Talent SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>52.004.665-8</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>19489.06</v>
+        <v>21037.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057387-140-CM25</t>
+          <t>585-41-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,17 +1603,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1623,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>NOVIS</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>96.967.100-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,7 +1638,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>21037.11</v>
+        <v>28905.3</v>
       </c>
     </row>
     <row r="20">
@@ -1673,7 +1705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>598-29-CM25</t>
+          <t>1051173-5-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,12 +1730,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>60.100.003-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1745,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>87364.12</v>
+        <v>27364.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1051173-5-CM25</t>
+          <t>598-29-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1795,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.100.003-2</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1810,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>27364.86</v>
+        <v>87364.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1588-378-CM24</t>
+          <t>3834-69-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1860,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Smartnodus SpA</t>
+          <t>TOTALPACK LTDA.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.461.797-5</t>
+          <t>79.948.840-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1890,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>25673.26</v>
+        <v>8655.459999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1973-1722-CM25</t>
+          <t>2341-144-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,17 +1916,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1936,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1951,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36794.57</v>
+        <v>8614.540000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5148-14-CM25</t>
+          <t>1588-378-CM24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1982,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1997,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SPIELUP SPA</t>
+          <t>Smartnodus SpA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.582.047-2</t>
+          <t>76.461.797-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2012,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>42539.49</v>
+        <v>25673.26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2341-144-CM25</t>
+          <t>1973-1722-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +2038,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>61.953.200-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2058,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2073,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8614.540000000001</v>
+        <v>36794.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3834-69-CM25</t>
+          <t>5148-14-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,27 +2104,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TOTALPACK LTDA.</t>
+          <t>SPIELUP SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>79.948.840-k</t>
+          <t>76.582.047-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2134,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8655.459999999999</v>
+        <v>42539.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2268-45-CM25</t>
+          <t>1436381-3-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2165,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2180,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2195,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>327494.66</v>
+        <v>41049.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1436381-3-CM25</t>
+          <t>603663-82-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,17 +2221,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2241,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2256,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41049.83</v>
+        <v>32076</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>603663-82-CM25</t>
+          <t>603663-83-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2262,28 +2302,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>32076</v>
+        <v>45908.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>603663-83-CM25</t>
+          <t>2268-45-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2347,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,22 +2367,26 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>45908.09</v>
+        <v>327494.66</v>
       </c>
     </row>
     <row r="32">
@@ -2527,7 +2575,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>630-29-CM25</t>
+          <t>2268-53-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,17 +2595,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.501.000-6</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL TRABAJO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2615,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2630,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>36890.26</v>
+        <v>18870.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3328-906-CM25</t>
+          <t>630-29-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,12 +2661,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.501.000-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SUBSECRETARIA DEL TRABAJO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2676,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INDRA SISTEMAS CHILE S.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.851.110-6</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>35976.06</v>
+        <v>36890.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2268-53-CM25</t>
+          <t>3328-906-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,17 +2721,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2741,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>INDRA SISTEMAS CHILE S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
+          <t>96.851.110-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,7 +2756,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>18870.52</v>
+        <v>35976.06</v>
       </c>
     </row>
     <row r="38">
@@ -2758,7 +2810,11 @@
           <t>76.227.643-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2771,7 +2827,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3810-756-CM25</t>
+          <t>730566-108-SE25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2852,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>19985.04</v>
+        <v>34047.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2268-40-CM25</t>
+          <t>3810-756-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,37 +2907,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IT4U</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.877.740-3</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2947,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>26887.43</v>
+        <v>19985.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5574-19-CM25</t>
+          <t>2268-40-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2968,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2993,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>IT4U</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.877.740-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,7 +3008,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>22003.04</v>
+        <v>26887.43</v>
       </c>
     </row>
     <row r="42">
@@ -3002,7 +3062,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3015,62 +3079,196 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>5574-19-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>22003.04</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>45-50-CM25</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>mar-2025</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>61.531.000-K</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
         <v>35305.18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1057547-17093-SE25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>46709.67</v>
       </c>
     </row>
   </sheetData>
